--- a/Employee_Reports_wi48/Yuvashanth Somasuntharam kukasuthan Q0560.xlsx
+++ b/Employee_Reports_wi48/Yuvashanth Somasuntharam kukasuthan Q0560.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-32</v>
+        <v>-35</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-46</v>
+        <v>-49</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-80</v>
+        <v>-83</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-33</v>
+        <v>-36</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-284</v>
+        <v>-287</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1265,11 +1265,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-130</v>
+        <v>-133</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-76</v>
+        <v>-79</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-340</v>
+        <v>-343</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1400,11 +1400,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-340</v>
+        <v>-343</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1437,11 +1437,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-130</v>
+        <v>-133</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-144</v>
+        <v>-147</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1523,11 +1523,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1597,11 +1597,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1634,11 +1634,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
